--- a/Tracking Data/PicoTracker.xlsx
+++ b/Tracking Data/PicoTracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidthrower/Documents/My Documents/Claude Context/Pico Balloons/Tracking Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{88B6D1F2-F4B6-3C4C-9671-3BF468373BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C985D72F-C773-684C-832A-A7658FC69693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4360" yWindow="680" windowWidth="30200" windowHeight="20160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker" sheetId="1" r:id="rId1"/>
@@ -230,7 +230,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -693,7 +693,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="3" width="21.33203125" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" style="5" customWidth="1"/>
@@ -713,28 +713,28 @@
     <col min="24" max="24" width="73.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="19" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:24" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="19" customHeight="1">
       <c r="A2" s="2">
         <v>46203</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
     </row>
-    <row r="6" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" s="7" customFormat="1">
       <c r="B6" s="7" t="s">
         <v>57</v>
       </c>
@@ -763,7 +763,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" s="7" customFormat="1">
       <c r="A7" s="7" t="s">
         <v>34</v>
       </c>
@@ -834,7 +834,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24">
       <c r="A8" s="5">
         <v>1</v>
       </c>
@@ -842,7 +842,7 @@
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="5">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>25</v>
@@ -864,7 +864,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24">
       <c r="A9" s="5">
         <v>2</v>
       </c>
@@ -889,7 +889,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24">
       <c r="A10" s="5">
         <v>3</v>
       </c>
@@ -914,7 +914,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="51" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" ht="51">
       <c r="A11" s="5">
         <v>4</v>
       </c>
@@ -949,7 +949,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="51" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" ht="51">
       <c r="A12" s="5">
         <v>5</v>
       </c>
@@ -984,7 +984,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1005,17 +1005,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE71AB22-6A7E-FB44-9621-B06B132CDAE6}">
   <dimension ref="B3:I9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="9" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:8">
       <c r="F3" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="2:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:8" s="7" customFormat="1">
       <c r="B4" s="7" t="s">
         <v>34</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:8">
       <c r="B6" s="5">
         <v>2</v>
       </c>
@@ -1073,7 +1073,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:8">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:8">
       <c r="B8" s="5">
         <v>4</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:8">
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -1135,7 +1135,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -1145,22 +1145,22 @@
     <col min="6" max="6" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="19">
       <c r="A1" s="12" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6">
       <c r="A2" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6">
       <c r="A5" s="9" t="s">
         <v>34</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="150" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="150" customHeight="1">
       <c r="A6" s="14" t="s">
         <v>38</v>
       </c>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="F6" s="15"/>
     </row>
-    <row r="7" spans="1:6" ht="150" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="150" customHeight="1">
       <c r="A7" s="14" t="s">
         <v>40</v>
       </c>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="F7" s="15"/>
     </row>
-    <row r="8" spans="1:6" ht="150" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="150" customHeight="1">
       <c r="A8" s="14" t="s">
         <v>42</v>
       </c>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F8" s="15"/>
     </row>
-    <row r="9" spans="1:6" ht="150" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="150" customHeight="1">
       <c r="A9" s="14" t="s">
         <v>44</v>
       </c>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="F9" s="15"/>
     </row>
-    <row r="10" spans="1:6" ht="150" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="150" customHeight="1">
       <c r="A10" s="14" t="s">
         <v>46</v>
       </c>
